--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.25177368647985</v>
+        <v>11.09091322405298</v>
       </c>
       <c r="D2" t="n">
-        <v>69.40961294764858</v>
+        <v>11.2790621039929</v>
       </c>
       <c r="E2" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F2" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.04103315762265</v>
+        <v>8.456667888113682</v>
       </c>
       <c r="D3" t="n">
-        <v>53.20085278813497</v>
+        <v>8.645138578071933</v>
       </c>
       <c r="E3" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F3" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.83566346828495</v>
+        <v>7.448295313596304</v>
       </c>
       <c r="D4" t="n">
-        <v>44.42010120615204</v>
+        <v>7.218266445999706</v>
       </c>
       <c r="E4" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F4" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.53076796306503</v>
+        <v>4.961249793998067</v>
       </c>
       <c r="D5" t="n">
-        <v>31.80259003882723</v>
+        <v>5.167920881309425</v>
       </c>
       <c r="E5" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F5" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.493029821100871</v>
+        <v>1.542617345928892</v>
       </c>
       <c r="D6" t="n">
-        <v>10.90959594071204</v>
+        <v>1.772809340365707</v>
       </c>
       <c r="E6" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F6" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.564410304607162</v>
+        <v>0.7417166744986639</v>
       </c>
       <c r="D7" t="n">
-        <v>4.317397549939678</v>
+        <v>0.7015771018651977</v>
       </c>
       <c r="E7" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F7" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.38242612290205</v>
+        <v>8.187144244971583</v>
       </c>
       <c r="D8" t="n">
-        <v>51.78917662601023</v>
+        <v>8.415741201726663</v>
       </c>
       <c r="E8" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F8" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.83844249289933</v>
+        <v>3.87374690509614</v>
       </c>
       <c r="D9" t="n">
-        <v>25.0245623156579</v>
+        <v>4.066491376294409</v>
       </c>
       <c r="E9" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F9" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.96744033063304</v>
+        <v>3.732209053727869</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34080428809404</v>
+        <v>3.792880696815282</v>
       </c>
       <c r="E10" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F10" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.33105143974559</v>
+        <v>3.466295858958659</v>
       </c>
       <c r="D11" t="n">
-        <v>21.63117870232298</v>
+        <v>3.515066539127485</v>
       </c>
       <c r="E11" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F11" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>11.65186274767844</v>
+        <v>1.893427696497746</v>
       </c>
       <c r="D12" t="n">
-        <v>10.57905885696793</v>
+        <v>1.719097064257289</v>
       </c>
       <c r="E12" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F12" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.76895348115843</v>
+        <v>1.912454940688245</v>
       </c>
       <c r="D13" t="n">
-        <v>9.072454121518023</v>
+        <v>1.474273794746679</v>
       </c>
       <c r="E13" t="n">
-        <v>19.38665284092083</v>
+        <v>3.150331086649635</v>
       </c>
       <c r="F13" t="n">
-        <v>19.90388641625612</v>
+        <v>3.23438154264162</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
